--- a/Backlog.xlsx
+++ b/Backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tobiaspottier/Main/Schoo/IndustryProject/IndustryProject-BeriatricSurgeryG1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CFB355-7842-9046-A0CE-4652D0706064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48F7FB83-6AA5-1542-A378-85A17C1B07FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17640" activeTab="3" xr2:uid="{00BCB2CB-A43B-3F46-B7C1-57D73B7C226B}"/>
   </bookViews>
